--- a/HayPriceLookup.xlsx
+++ b/HayPriceLookup.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HayData" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lists" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Lookup" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Detail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HayData" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lists" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lookup" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="About" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -115,13 +117,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -495,28 +497,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>USDA Hay Prices — Raw Survey Data (2025, $/ton)</t>
+          <t>Source Detail — USDA AMS Direct Hay Reports (per-ton rows, Good-band Alfalfa)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: USDA NASS, "Hay prices state June-Sept.csv" (periods Jun–Oct 2025). HAY - PRICE RECEIVED, MEASURED IN $/TON.</t>
+          <t>Class=Alfalfa; Quality in (Good, Fair/Good, Good/Premium); Per-Ton only. Latest report within 8 weeks (since 07/06/2026). Pulled 08/31/2026 from USDA AMS MARS API.</t>
         </is>
       </c>
     </row>
@@ -528,22 +534,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Period Begin</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Price ($/ton)</t>
+          <t>Period End</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Class</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Avg Price ($/ton)</t>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Price Min</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Price Max</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Wtd Avg (reported)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Effective $/ton (used)</t>
         </is>
       </c>
     </row>
@@ -555,115 +586,216 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>190</v>
+          <t>07/20/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>07/24/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="F5" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E5,$C$5:$C$139)</f>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <f>IF(I5=0,(G5+H5)/2,I5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>180</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F6" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E6,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>North Inter-Mountains</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="J6" s="5">
+        <f>IF(I6=0,(G6+H6)/2,I6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>170</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Colorado</t>
-        </is>
-      </c>
-      <c r="F7" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E7,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>North Inter-Mountains</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>191.92</v>
+      </c>
+      <c r="J7" s="5">
+        <f>IF(I7=0,(G7+H7)/2,I7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>North San Joaquin Valley</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Idaho</t>
-        </is>
-      </c>
-      <c r="F8" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E8,$C$5:$C$139)</f>
+      <c r="H8" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="J8" s="5">
+        <f>IF(I8=0,(G8+H8)/2,I8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>189</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Illinois</t>
-        </is>
-      </c>
-      <c r="F9" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E9,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>North San Joaquin Valley</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>203.46</v>
+      </c>
+      <c r="J9" s="5">
+        <f>IF(I9=0,(G9+H9)/2,I9)</f>
         <v/>
       </c>
     </row>
@@ -675,19 +807,40 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>228</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-      <c r="F10" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E10,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="J10" s="5">
+        <f>IF(I10=0,(G10+H10)/2,I10)</f>
         <v/>
       </c>
     </row>
@@ -699,545 +852,1072 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>225</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="F11" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E11,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J11" s="5">
+        <f>IF(I11=0,(G11+H11)/2,I11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>218</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="F12" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E12,$C$5:$C$139)</f>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Northeast</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>335</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>335</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>335</v>
+      </c>
+      <c r="J12" s="5">
+        <f>IF(I12=0,(G12+H12)/2,I12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>221</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-      <c r="F13" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E13,$C$5:$C$139)</f>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="J13" s="5">
+        <f>IF(I13=0,(G13+H13)/2,I13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>224</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Minnesota</t>
-        </is>
-      </c>
-      <c r="F14" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E14,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="J14" s="5">
+        <f>IF(I14=0,(G14+H14)/2,I14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>149</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Missouri</t>
-        </is>
-      </c>
-      <c r="F15" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E15,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="J15" s="5">
+        <f>IF(I15=0,(G15+H15)/2,I15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>159</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Montana</t>
-        </is>
-      </c>
-      <c r="F16" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E16,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="J16" s="5">
+        <f>IF(I16=0,(G16+H16)/2,I16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>154</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
-      <c r="F17" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E17,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="J17" s="5">
+        <f>IF(I17=0,(G17+H17)/2,I17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>168</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Nevada</t>
-        </is>
-      </c>
-      <c r="F18" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E18,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="J18" s="5">
+        <f>IF(I18=0,(G18+H18)/2,I18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>184</v>
+          <t>07/27/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
-      <c r="F19" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E19,$C$5:$C$139)</f>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="J19" s="5">
+        <f>IF(I19=0,(G19+H19)/2,I19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>160</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F20" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E20,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>North Central</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="J20" s="5">
+        <f>IF(I20=0,(G20+H20)/2,I20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>156</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>North Dakota</t>
-        </is>
-      </c>
-      <c r="F21" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E21,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>North Central</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J21" s="5">
+        <f>IF(I21=0,(G21+H21)/2,I21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>157</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="F22" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E22,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>North Central</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="J22" s="5">
+        <f>IF(I22=0,(G22+H22)/2,I22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>158</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="F23" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E23,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>North Central</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>180.27</v>
+      </c>
+      <c r="J23" s="5">
+        <f>IF(I23=0,(G23+H23)/2,I23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>153</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="F24" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E24,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>North Central</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="J24" s="5">
+        <f>IF(I24=0,(G24+H24)/2,I24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>140</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="F25" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E25,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>North Central</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J25" s="5">
+        <f>IF(I25=0,(G25+H25)/2,I25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>140</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-      <c r="F26" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E26,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Northwest</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="J26" s="5">
+        <f>IF(I26=0,(G26+H26)/2,I26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>142</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="F27" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E27,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Northwest</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="J27" s="5">
+        <f>IF(I27=0,(G27+H27)/2,I27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>145</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="F28" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E28,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="J28" s="5">
+        <f>IF(I28=0,(G28+H28)/2,I28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>138</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="F29" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E29,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>200.32</v>
+      </c>
+      <c r="J29" s="5">
+        <f>IF(I29=0,(G29+H29)/2,I29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>99</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="F30" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E30,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>192.78</v>
+      </c>
+      <c r="J30" s="5">
+        <f>IF(I30=0,(G30+H30)/2,I30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>91</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="F31" s="6">
-        <f>AVERAGEIF($A$5:$A$139,E31,$C$5:$C$139)</f>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="J31" s="5">
+        <f>IF(I31=0,(G31+H31)/2,I31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>100</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="J32" s="5">
+        <f>IF(I32=0,(G32+H32)/2,I32)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>102</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>246.47</v>
+      </c>
+      <c r="J33" s="5">
+        <f>IF(I33=0,(G33+H33)/2,I33)</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>105</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J34" s="5">
+        <f>IF(I34=0,(G34+H34)/2,I34)</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1248,11 +1928,41 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>116</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J35" s="5">
+        <f>IF(I35=0,(G35+H35)/2,I35)</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1263,11 +1973,41 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>118</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="J36" s="5">
+        <f>IF(I36=0,(G36+H36)/2,I36)</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1278,11 +2018,41 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>118</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>194.87</v>
+      </c>
+      <c r="J37" s="5">
+        <f>IF(I37=0,(G37+H37)/2,I37)</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1293,11 +2063,41 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>115</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J38" s="5">
+        <f>IF(I38=0,(G38+H38)/2,I38)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1308,296 +2108,896 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>116</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>201.82</v>
+      </c>
+      <c r="J39" s="5">
+        <f>IF(I39=0,(G39+H39)/2,I39)</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>184</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="J40" s="5">
+        <f>IF(I40=0,(G40+H40)/2,I40)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n">
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
         <v>195</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>198.33</v>
+      </c>
+      <c r="J41" s="5">
+        <f>IF(I41=0,(G41+H41)/2,I41)</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>199</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J42" s="5">
+        <f>IF(I42=0,(G42+H42)/2,I42)</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>208</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>245.71</v>
+      </c>
+      <c r="J43" s="5">
+        <f>IF(I43=0,(G43+H43)/2,I43)</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>203</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>260.37</v>
+      </c>
+      <c r="J44" s="5">
+        <f>IF(I44=0,(G44+H44)/2,I44)</f>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>149</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>230.13</v>
+      </c>
+      <c r="J45" s="5">
+        <f>IF(I45=0,(G45+H45)/2,I45)</f>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>147</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="J46" s="5">
+        <f>IF(I46=0,(G46+H46)/2,I46)</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>151</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="J47" s="5">
+        <f>IF(I47=0,(G47+H47)/2,I47)</f>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>150</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="J48" s="5">
+        <f>IF(I48=0,(G48+H48)/2,I48)</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>146</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="J49" s="5">
+        <f>IF(I49=0,(G49+H49)/2,I49)</f>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>92</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="J50" s="5">
+        <f>IF(I50=0,(G50+H50)/2,I50)</f>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>86</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J51" s="5">
+        <f>IF(I51=0,(G51+H51)/2,I51)</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>89</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>204.17</v>
+      </c>
+      <c r="J52" s="5">
+        <f>IF(I52=0,(G52+H52)/2,I52)</f>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>94</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="J53" s="5">
+        <f>IF(I53=0,(G53+H53)/2,I53)</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>88</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="J54" s="5">
+        <f>IF(I54=0,(G54+H54)/2,I54)</f>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>124</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>South Central</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>268.35</v>
+      </c>
+      <c r="J55" s="5">
+        <f>IF(I55=0,(G55+H55)/2,I55)</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>123</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="J56" s="5">
+        <f>IF(I56=0,(G56+H56)/2,I56)</f>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>118</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="J57" s="5">
+        <f>IF(I57=0,(G57+H57)/2,I57)</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>122</v>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Southwest</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="J58" s="5">
+        <f>IF(I58=0,(G58+H58)/2,I58)</f>
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -1608,11 +3008,37 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>124</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="5">
+        <f>IF(I59=0,(G59+H59)/2,I59)</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -1623,71 +3049,217 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>143</v>
+          <t>07/20/2026</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>07/24/2026</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="J60" s="5">
+        <f>IF(I60=0,(G60+H60)/2,I60)</f>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>144</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="J61" s="5">
+        <f>IF(I61=0,(G61+H61)/2,I61)</f>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>147</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="J62" s="5">
+        <f>IF(I62=0,(G62+H62)/2,I62)</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>142</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Platte Valley</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>201.25</v>
+      </c>
+      <c r="J63" s="5">
+        <f>IF(I63=0,(G63+H63)/2,I63)</f>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>137</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Platte Valley</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="J64" s="5">
+        <f>IF(I64=0,(G64+H64)/2,I64)</f>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -1698,11 +3270,41 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>98</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>270.42</v>
+      </c>
+      <c r="J65" s="5">
+        <f>IF(I65=0,(G65+H65)/2,I65)</f>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -1713,11 +3315,41 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>96</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="J66" s="5">
+        <f>IF(I66=0,(G66+H66)/2,I66)</f>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -1728,11 +3360,41 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>97</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="J67" s="5">
+        <f>IF(I67=0,(G67+H67)/2,I67)</f>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -1743,26 +3405,86 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>97</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>326.67</v>
+      </c>
+      <c r="J68" s="5">
+        <f>IF(I68=0,(G68+H68)/2,I68)</f>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>98</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="J69" s="5">
+        <f>IF(I69=0,(G69+H69)/2,I69)</f>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -1773,11 +3495,41 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>170</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="J70" s="5">
+        <f>IF(I70=0,(G70+H70)/2,I70)</f>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -1788,11 +3540,41 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="n">
-        <v>161</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="J71" s="5">
+        <f>IF(I71=0,(G71+H71)/2,I71)</f>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -1803,11 +3585,41 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>165</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>195.45</v>
+      </c>
+      <c r="J72" s="5">
+        <f>IF(I72=0,(G72+H72)/2,I72)</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -1818,11 +3630,41 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>161</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="J73" s="5">
+        <f>IF(I73=0,(G73+H73)/2,I73)</f>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -1833,11 +3675,41 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>161</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="J74" s="5">
+        <f>IF(I74=0,(G74+H74)/2,I74)</f>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -1848,11 +3720,41 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>229</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Northwest</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="5">
+        <f>IF(I75=0,(G75+H75)/2,I75)</f>
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -1863,11 +3765,41 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>235</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Northwest</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="5">
+        <f>IF(I76=0,(G76+H76)/2,I76)</f>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -1878,941 +3810,962 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>236</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="5">
+        <f>IF(I77=0,(G77+H77)/2,I77)</f>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>242</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="5">
+        <f>IF(I78=0,(G78+H78)/2,I78)</f>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>251</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J79" s="5">
+        <f>IF(I79=0,(G79+H79)/2,I79)</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>208</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Northwest</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5">
+        <f>IF(I80=0,(G80+H80)/2,I80)</f>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>196</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Northwest</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="J81" s="5">
+        <f>IF(I81=0,(G81+H81)/2,I81)</f>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>187</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Lake County</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="J82" s="5">
+        <f>IF(I82=0,(G82+H82)/2,I82)</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="n">
-        <v>189</v>
+          <t>07/27/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>07/31/2026</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J83" s="5">
+        <f>IF(I83=0,(G83+H83)/2,I83)</f>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="n">
-        <v>201</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="J84" s="5">
+        <f>IF(I84=0,(G84+H84)/2,I84)</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="n">
-        <v>90</v>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>08/28/2026</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>246.24</v>
+      </c>
+      <c r="J85" s="5">
+        <f>IF(I85=0,(G85+H85)/2,I85)</f>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="n">
-        <v>88</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="J86" s="5">
+        <f>IF(I86=0,(G86+H86)/2,I86)</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="n">
-        <v>86</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="n"/>
+      <c r="G87" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="J87" s="5">
+        <f>IF(I87=0,(G87+H87)/2,I87)</f>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="n">
-        <v>86</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="n"/>
+      <c r="G88" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="J88" s="5">
+        <f>IF(I88=0,(G88+H88)/2,I88)</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="n">
-        <v>83</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="J89" s="5">
+        <f>IF(I89=0,(G89+H89)/2,I89)</f>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="n">
-        <v>190</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="J90" s="5">
+        <f>IF(I90=0,(G90+H90)/2,I90)</f>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="n">
-        <v>180</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="J91" s="5">
+        <f>IF(I91=0,(G91+H91)/2,I91)</f>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="n">
-        <v>175</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="J92" s="5">
+        <f>IF(I92=0,(G92+H92)/2,I92)</f>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="n">
-        <v>176</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="J93" s="5">
+        <f>IF(I93=0,(G93+H93)/2,I93)</f>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>180</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>266.67</v>
+      </c>
+      <c r="J94" s="5">
+        <f>IF(I94=0,(G94+H94)/2,I94)</f>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="n">
-        <v>104</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="J95" s="5">
+        <f>IF(I95=0,(G95+H95)/2,I95)</f>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>93</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="J96" s="5">
+        <f>IF(I96=0,(G96+H96)/2,I96)</f>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>95</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="J97" s="5">
+        <f>IF(I97=0,(G97+H97)/2,I97)</f>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="n">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="n">
-        <v>150</v>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>08/21/2026</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Alfalfa</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="J98" s="5">
+        <f>IF(I98=0,(G98+H98)/2,I98)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2821,6 +4774,493 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Average Hay Price by State — $/ton (Good-band Alfalfa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Basis: USDA AMS Direct Hay Reports, Alfalfa graded Good / Fair-Good / Good-Premium, per ton, latest report within 8 weeks (since 07/06/2026). Generated 08/31/2026. Averages computed from the Detail tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Avg Price ($/ton)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Report Period</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Grades Used</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t># Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A5,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>07/20/2026-07/24/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="E5" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A6,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>08/24/2026-08/28/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good, Good</t>
+        </is>
+      </c>
+      <c r="E6" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A7,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>08/24/2026-08/28/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="E7" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A8,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>08/17/2026-08/21/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E8" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A9,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>07/27/2026-07/31/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E9" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A10,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>08/10/2026-08/14/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good, Good</t>
+        </is>
+      </c>
+      <c r="E10" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A11,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>08/17/2026-08/21/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E11" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A12,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>07/20/2026-07/24/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="E12" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A13,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>08/24/2026-08/28/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Good, Good/Premium</t>
+        </is>
+      </c>
+      <c r="E13" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A14,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>08/17/2026-08/21/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Good, Good/Premium</t>
+        </is>
+      </c>
+      <c r="E14" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="B15" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A15,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>08/24/2026-08/28/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E15" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A16,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>08/17/2026-08/21/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good, Good, Good/Premium</t>
+        </is>
+      </c>
+      <c r="E16" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A17,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>08/24/2026-08/28/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E17" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="B18" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A18,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>07/27/2026-07/31/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Good/Premium</t>
+        </is>
+      </c>
+      <c r="E18" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A19,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>08/24/2026-08/28/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Good, Good/Premium</t>
+        </is>
+      </c>
+      <c r="E19" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="B20" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A20,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>08/17/2026-08/21/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good, Good/Premium</t>
+        </is>
+      </c>
+      <c r="E20" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B21" s="5">
+        <f>AVERAGEIF(Detail!$A$5:$A$98,A21,Detail!$J$5:$J$98)</f>
+        <v/>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>08/17/2026-08/21/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Fair/Good, Good, Good/Premium</t>
+        </is>
+      </c>
+      <c r="E21" s="6">
+        <f>COUNTIF(Detail!$A$5:$A$98,A21)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2835,7 +5275,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>State (for dropdown)</t>
+          <t>State (dropdown source)</t>
         </is>
       </c>
     </row>
@@ -3201,18 +5641,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3225,7 +5665,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Pick a State from the dropdown in the yellow cell. The average hay price auto-populates in the green cell.</t>
+          <t>Pick a State (yellow cell). Average hay price auto-populates (green). County dropdown to be added later.</t>
         </is>
       </c>
     </row>
@@ -3250,7 +5690,7 @@
       <c r="B6" s="9" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>(county dropdown to be added — does not affect hay price)</t>
+          <t>(does not affect hay price — state-level basis)</t>
         </is>
       </c>
     </row>
@@ -3261,16 +5701,151 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>IF($B$5="","",IFERROR(INDEX(HayData!$F$5:$F$31,MATCH($B$5,HayData!$E$5:$E$31,0)),"no hay price data available for "&amp;$B$5&amp;", manual entry required"))</f>
+        <f>IF($B$5="","",IFERROR(INDEX(HayData!$B$5:$B$21,MATCH($B$5,HayData!$A$5:$A$21,0)),"no hay price data available for "&amp;$B$5&amp;", manual entry required"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Report Period:</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>IF($B$5="","",IFERROR(INDEX(HayData!$C$5:$C$21,MATCH($B$5,HayData!$A$5:$A$21,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Grades Used:</t>
+        </is>
+      </c>
+      <c r="B10" s="6">
+        <f>IF($B$5="","",IFERROR(INDEX(HayData!$D$5:$D$21,MATCH($B$5,HayData!$A$5:$A$21,0)),""))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a state from the list." prompt="Select a state" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Select a state" type="list">
       <formula1>=Lists!$A$2:$A$52</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hay Price Lookup — Data Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Generated: 08/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Source: USDA AMS Livestock, Poultry &amp; Grain Market News — state Direct Hay Reports (via MARS API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Basis: Alfalfa hay, grades Good / Fair-Good / Good-Premium, priced Per Ton.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>For each state, the most recent report within an 8-week freshness window is used;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>all qualifying per-ton rows (across regions/grades) are averaged into one $/ton figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Rows with no established trade (reported weighted avg = 0) use the midpoint of the price range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Coverage: 17 of 21 states that publish Direct Hay Reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>No per-ton data (return manual-entry message): Alabama, Kentucky, Tennessee report only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>per-bale prices; Texas had no Good-band alfalfa per-ton row within the 8-week window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>All other U.S. states have no USDA Direct Hay Report and return the manual-entry message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Washington figure is sourced from the Washington-Oregon (Columbia Basin) Direct Hay Report.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>